--- a/artfynd/A 17018-2023 artfynd.xlsx
+++ b/artfynd/A 17018-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17018-2023 artfynd.xlsx
+++ b/artfynd/A 17018-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113566728</v>
+        <v>103696862</v>
       </c>
       <c r="B2" t="n">
-        <v>104650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>1100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rosetticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hallsberg-timmersdala, Nrk</t>
+          <t>Nygårdvulkanens kalkbarrskog NR, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492900</v>
+        <v>492586</v>
       </c>
       <c r="R2" t="n">
-        <v>6541015</v>
+        <v>6540760</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tunna hattar, hymeniet tunt, poroid, ca 7 porer/mm. Sporer lättovala ca 4 x 3 µm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,15 +765,415 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann, Camilla Pettersson, Anders Carlberg, Joakim Johansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113566728</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hallsberg-timmersdala, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>492900</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6541015</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Andreas Källman</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Andreas Källman</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113566725</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hallsberg-timmersdala, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>493015</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6541026</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120714728</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Askersund-Tycke, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>493024</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6541036</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Snavlunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>INN0003 Askersund-Tycke NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121142753</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>493010</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6541032</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17018-2023 artfynd.xlsx
+++ b/artfynd/A 17018-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103696862</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113566728</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113566725</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
           <t>INN0003 Askersund-Tycke NVI</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120714728</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,8 +1199,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121142753</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>